--- a/results/reliability_eval/reliability_eval_typo-test-09-30/Llama-3-8B_P17_char_substitution_typo3_sample_tok25_temp0.1_direct_completion_rep5_beams5_maxent20_rows100_scores_typo-test-09-30.xlsx
+++ b/results/reliability_eval/reliability_eval_typo-test-09-30/Llama-3-8B_P17_char_substitution_typo3_sample_tok25_temp0.1_direct_completion_rep5_beams5_maxent20_rows100_scores_typo-test-09-30.xlsx
@@ -512,52 +512,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.9036144578313253</v>
+        <v>0.7762725779967159</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9717472884349998</v>
+        <v>0.6598725208893876</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1392308647828401</v>
+        <v>0.2298942723756063</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4142650214246024</v>
+        <v>3.978143356920662</v>
       </c>
       <c r="E2" t="n">
-        <v>24.69406194659699</v>
+        <v>28.08153178200787</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7019844082211198</v>
+        <v>0.6941707717569786</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9367788191379379</v>
+        <v>0.626336885286344</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1565154969828005</v>
+        <v>0.5272310464088444</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5357162217335157</v>
+        <v>5.084383553007455</v>
       </c>
       <c r="J2" t="n">
-        <v>6.332315016553244</v>
+        <v>5.276172191371237</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9766123316796598</v>
+        <v>0.9987684729064039</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9932907066863947</v>
+        <v>0.9968253968253968</v>
       </c>
       <c r="M2" t="n">
-        <v>0.044</v>
+        <v>0.012</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1259718712282981</v>
+        <v>0.03365058335046304</v>
       </c>
       <c r="O2" t="n">
-        <v>9.820537243229822</v>
+        <v>2.643856183282597</v>
       </c>
       <c r="P2" t="n">
-        <v>0.83</v>
+        <v>0.42</v>
       </c>
     </row>
   </sheetData>
